--- a/www/flightdata/xlsx/eoss-324.xlsx
+++ b/www/flightdata/xlsx/eoss-324.xlsx
@@ -3771,7 +3771,7 @@
         <v>28182.42</v>
       </c>
       <c r="I2">
-        <v>659</v>
+        <v>492</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
